--- a/validation_2010_age45/edge_validation.xlsx
+++ b/validation_2010_age45/edge_validation.xlsx
@@ -203,7 +203,7 @@
       </c>
       <c r="G3" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The adult review describes longstanding attentional, emotional-regulation, and disinhibition impairments, consistent with executive dysfunction, but does not identify ADHD as a separate causal exposure.</t>
+          <t xml:space="preserve">The adult review describes longstanding attentional, emotional-regulation, and disinhibition impairments, consistent with executive dysfunction, but does not identify ADHD as a separate causal exposure. The new adult ERP review adds cognitive-processing context without isolating the practical functional consequences of executive deficits at midlife.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="0">
@@ -215,7 +215,10 @@
         <is>
           <t xml:space="preserve">ADULT_CBT: Resulting from their longstanding neuropsychological impairments, such as attentional problems, emotional instability, and disinhibition, they are familiar to a multiplicity of negative life outcomes and under-achievement.
 Location: PDF page 1
-Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.</t>
+Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.
+PMID_20660947: Considering that all three core symptoms of the disorder have a significant impact on both information processing and on concomitant cognitive functions, patients with ADHD should be divided into subgroups based on their neuropsychologically measured dominant symptoms.
+Location: [Event-related potentials associated with error detection in adult ADHD--literature review] - PubMed.html; article abstract (#eng-abstract)
+Relevance: Adult electrophysiological review: cognitive processing mechanisms, not a controlled executive-deficit-to-practical-impairment effect.</t>
         </is>
       </c>
     </row>
@@ -252,19 +255,25 @@
       </c>
       <c r="G4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The adult review reports frequent psychiatric comorbidity, but co-occurrence does not establish ADHD as its cause.</t>
+          <t xml:space="preserve">New adult bipolar and prison studies document comorbidity and symptom overlap in selected samples. This strengthens adult co-occurrence evidence, but does not show ADHD causing those conditions or supply an exact-age estimate.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Represent this as an association or specify a comorbid outcome and mechanism.</t>
+          <t xml:space="preserve">Retain as an association with named comorbidities; distinguish screening results and selected populations from causal mechanisms.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ADULT_CBT: Furthermore, a large part of this population suffers from psychiatric comorbidity.
 Location: PDF page 1
-Relevance: Supports adult co-occurrence, not ADHD causing each comorbid condition.</t>
+Relevance: Supports adult co-occurrence, not ADHD causing each comorbid condition.
+BIPOLAR_ADULT: Conclusions: Our findings illustrate the close relationship between some symptoms of BSD and ADHD in adults.
+Location: Bipolar Symptoms in Adult Attention-Deficit_Hyperactivity Disorder_ A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls.html; article abstract (#article-tabs)
+Relevance: Cross-sectional adult symptom overlap; screening positive is not identical to confirmed bipolar disorder. Clinical assessment ambiguity is supported but actual diagnostic error rates and causation are unmeasured.
+PMID_19270267: The authors conclude that ADHD is common in offenders and is associated with comorbid disorders, worse quality of life, and higher risk for suicidal behaviors.
+Location: Attention deficit hyperactivity disorder in men and women newly committed to prison_ clinical characteristics, psychiatric comorbidity, and quality of life - PubMed.html; article abstract (#eng-abstract)
+Relevance: Selected incarcerated adult sample; not representative of all adults. Association of ADHD with QOL does not isolate functional impairment as a cause or diagnosis as a benefit.</t>
         </is>
       </c>
     </row>
@@ -301,7 +310,7 @@
       </c>
       <c r="G5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Longstanding neuropsychological impairments are linked with negative life outcomes and underachievement, but the evidence does not isolate executive dysfunction as the causal component.</t>
+          <t xml:space="preserve">Longstanding neuropsychological impairments are linked with negative life outcomes and underachievement, but the evidence does not isolate executive dysfunction as the causal component. The new adult ERP review adds cognitive-processing context without isolating the practical functional consequences of executive deficits at midlife.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr" s="0">
@@ -313,7 +322,10 @@
         <is>
           <t xml:space="preserve">ADULT_CBT: Resulting from their longstanding neuropsychological impairments, such as attentional problems, emotional instability, and disinhibition, they are familiar to a multiplicity of negative life outcomes and under-achievement.
 Location: PDF page 1
-Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.</t>
+Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.
+PMID_20660947: Considering that all three core symptoms of the disorder have a significant impact on both information processing and on concomitant cognitive functions, patients with ADHD should be divided into subgroups based on their neuropsychologically measured dominant symptoms.
+Location: [Event-related potentials associated with error detection in adult ADHD--literature review] - PubMed.html; article abstract (#eng-abstract)
+Relevance: Adult electrophysiological review: cognitive processing mechanisms, not a controlled executive-deficit-to-practical-impairment effect.</t>
         </is>
       </c>
     </row>
@@ -350,12 +362,12 @@
       </c>
       <c r="G6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The corpus relates persistent symptoms and neuropsychological difficulties to negative adult outcomes, but does not estimate a symptom-severity gradient at age 45.</t>
+          <t xml:space="preserve">The added prison and bipolar studies associate ADHD/comorbidity with emotional, social, educational and occupational problems. They do not isolate symptom severity as a causal exposure or estimate a general effect at this age.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain as a clinically coherent pathway while labeling its age-specific magnitude unvalidated.</t>
+          <t xml:space="preserve">Retain a qualified functional association and disclose selection, confounding and age coverage.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="0">
@@ -365,7 +377,13 @@
 Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.
 AGE_SEX: Although they may no longer meet the full symptom criterion, young adults with a history of lifetime DSM-IV-like ADHD maintain higher levels of ADHD symptoms compared to the general population.
 Location: PDF page 1
-Relevance: Supports symptom persistence with attenuation in young adults, but not a causal estimate at age 32.</t>
+Relevance: Supports symptom persistence with attenuation in young adults, but not a causal estimate at age 32.
+PMID_19270267: Offenders with ADHD were more likely to report problems with emotional and social functioning and to have higher suicide risk scores (p &lt; .001).
+Location: Attention deficit hyperactivity disorder in men and women newly committed to prison_ clinical characteristics, psychiatric comorbidity, and quality of life - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observed functional associations in prisoners; no symptom-severity intervention or age-32/45 estimate.
+BIPOLAR_ADULT: Patients screening positive on the MDQ had significantly more drug problems, higher ADHD symptom scores, and lower educational and occupational levels.
+Location: Bipolar Symptoms in Adult Attention-Deficit_Hyperactivity Disorder_ A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls.html; article abstract (#article-tabs)
+Relevance: Association between bipolar screening status and functional indicators; no causal effect, no exact age-32 estimate, and no midlife subgroup supplied.</t>
         </is>
       </c>
     </row>
@@ -449,17 +467,19 @@
       </c>
       <c r="G8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The nutritional abstract concerns children with ADHD/ASD and reports no effectiveness conclusion; it does not establish a nutrition effect in adults at this age.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult nutrition-intervention evidence with specific exposures and symptom outcomes.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21766545: This updated review presents the evidence regarding the usefulness and limitations of the most frequent nutritional and dietary interventions in the treatment of ADHD and/or ASD.
+Location: Effectiveness of nutritional interventions on the functioning of children with ADHD and_or ASD. An updated review of research evidence - PubMed.html; article abstract (#eng-abstract)
+Relevance: Abstract describes the review scope but supplies no efficacy conclusion, effect size or comparison supporting the direction of the nutrition edge.</t>
         </is>
       </c>
     </row>
@@ -825,17 +845,19 @@
       </c>
       <c r="G16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -872,17 +894,19 @@
       </c>
       <c r="G17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -919,17 +943,19 @@
       </c>
       <c r="G18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -966,17 +992,19 @@
       </c>
       <c r="G19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1088,19 @@
       </c>
       <c r="G21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -1436,17 +1466,19 @@
       </c>
       <c r="G29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -1968,17 +2000,19 @@
       </c>
       <c r="G40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -2015,17 +2049,19 @@
       </c>
       <c r="G41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -2062,17 +2098,19 @@
       </c>
       <c r="G42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new geographic and disparity papers concern pediatric diagnosis and treatment. They do not identify this access, bias, or treatment pathway in adults; child service patterns are not transferred to age-specific adult claims.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Require adult evidence on the specified access/bias exposure and actual service endpoint.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.</t>
         </is>
       </c>
     </row>
@@ -2438,19 +2476,22 @@
       </c>
       <c r="G50" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Medication is recommended for adults, but the supplied passages do not provide an age-45 controlled symptom effect.</t>
+          <t xml:space="preserve">The added stimulant review summarizes randomized efficacy evidence including adults, strengthening the earlier recommendation-based support. Exact-age effects and the graph’s broad medication magnitude are not supplied.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain the negative edge with a medication-specific midlife efficacy source before assigning magnitude.</t>
+          <t xml:space="preserve">Retain stimulant-specific symptom efficacy with adult age/outcome limits; do not validate numeric strength.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">CPG_REVIEW: The NICE guidelines recommend medication treatment as the first-line intervention for children, adolescents, and young adults with severe ADHD as well as for adults with ADHD
 Location: PDF page 5
-Relevance: Supports medication as recommended adult treatment, not the probability that diagnosis or access causes its use.</t>
+Relevance: Supports medication as recommended adult treatment, not the probability that diagnosis or access causes its use.
+PMID_20513225: Randomised controlled trials confirm that stimulant medication is efficacious for, and well tolerated by, males and females and patients across the age range; although preschoolers appear to have a less beneficial response and more side effects.
+Location: Stimulant drug effects on attention deficit_hyperactivity disorder_ a review of the effects of age and sex of patients - PubMed.html; article abstract (#eng-abstract)
+Relevance: Review of controlled stimulant trials including adulthood; broad age coverage without an estimate at exactly eight, 32 or 45. Tolerability does not mean no adverse effects.</t>
         </is>
       </c>
     </row>
@@ -2482,24 +2523,27 @@
       </c>
       <c r="F51" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G51" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Adult medication is recommended, but the supplied evidence does not estimate medication's effect on functional impairment at age 45.</t>
+          <t xml:space="preserve">The systematic medication review reports short-term QOL improvement in adults. QOL reflects perceived functioning and provides narrower treatment-benefit evidence, but is not a separately measured general functional-impairment outcome, and adult studies are few with no age-45 estimate.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Add an adult treatment study with a functional endpoint.</t>
+          <t xml:space="preserve">Retain only partial support from a related functioning/QOL endpoint; obtain a midlife medication trial with a defined impairment measure.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">CPG_REVIEW: The NICE guidelines recommend medication treatment as the first-line intervention for children, adolescents, and young adults with severe ADHD as well as for adults with ADHD
 Location: PDF page 5
-Relevance: Supports medication as recommended adult treatment, not the probability that diagnosis or access causes its use.</t>
+Relevance: Supports medication as recommended adult treatment, not the probability that diagnosis or access causes its use.
+PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -2778,15 +2822,67 @@
       </c>
       <c r="G57" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Stimulant medication guides list multiple adverse effects. The supporting paper concerns nonmedical college use, so it does not fully validate therapeutic treatment at age 45.</t>
+          <t xml:space="preserve">The stimulant review discusses tolerability and age-related adverse effects, but supplies no therapeutic adult adverse-event estimate at this age. The prior nonmedical-use evidence remains limited for clinical treatment.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain the positive edge, specifying drug, dose, and treatment context.</t>
+          <t xml:space="preserve">Specify medication, dose, treatment context and actual adverse-event population; tolerability is not absence of side effects.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">NONMEDICAL_STIMULANT: common side effects of the drugs include headache, stomach upset, nausea, loss of appetite, trouble sleeping, weight loss, dry mouth, nervousness, mood swings, dizziness, fast heart beat, and heart palpitations
+Location: PDF page 2
+Relevance: Supports stimulant adverse effects, although the paper studies nonmedical college use rather than prescribed treatment at age 32.
+PMID_20513225: Randomised controlled trials confirm that stimulant medication is efficacious for, and well tolerated by, males and females and patients across the age range; although preschoolers appear to have a less beneficial response and more side effects.
+Location: Stimulant drug effects on attention deficit_hyperactivity disorder_ a review of the effects of age and sex of patients - PubMed.html; article abstract (#eng-abstract)
+Relevance: Review of controlled stimulant trials including adulthood; broad age coverage without an estimate at exactly eight, 32 or 45. Tolerability does not mean no adverse effects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="110" customHeight="1">
+      <c r="A58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Treatment Side Effects</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Treatment Adherence</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Side effects can reduce adherence.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">insufficient_evidence</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The corpus documents adverse effects but does not show that they cause lower adherence in treated midlife adults.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Add direct discontinuation or adherence evidence.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NONMEDICAL_STIMULANT: common side effects of the drugs include headache, stomach upset, nausea, loss of appetite, trouble sleeping, weight loss, dry mouth, nervousness, mood swings, dizziness, fast heart beat, and heart palpitations
 Location: PDF page 2
@@ -2794,101 +2890,55 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="110" customHeight="1">
-      <c r="A58" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">57</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr" s="0">
+    <row r="59" ht="110" customHeight="1">
+      <c r="A59" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Treatment Side Effects</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Treatment Adherence</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Side effects can reduce adherence.</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr" s="0">
+      <c r="C59" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Quality of Life</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Side effects can slightly reduce quality of life.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr" s="0">
+      <c r="F59" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">insufficient_evidence</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">The corpus documents adverse effects but does not show that they cause lower adherence in treated midlife adults.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Add direct discontinuation or adherence evidence.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr" s="0">
+      <c r="G59" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The medication review reports overall QOL improvement, not an independent adverse-effect-to-QOL effect. Net treatment benefit does not establish or refute side effects lowering QOL.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Obtain separately measured adverse effects and longitudinal QOL data.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">NONMEDICAL_STIMULANT: common side effects of the drugs include headache, stomach upset, nausea, loss of appetite, trouble sleeping, weight loss, dry mouth, nervousness, mood swings, dizziness, fast heart beat, and heart palpitations
 Location: PDF page 2
-Relevance: Supports stimulant adverse effects, although the paper studies nonmedical college use rather than prescribed treatment at age 32.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="110" customHeight="1">
-      <c r="A59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">58</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Treatment Side Effects</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Quality of Life</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Side effects can slightly reduce quality of life.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">insufficient_evidence</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">The corpus documents adverse effects but does not estimate their independent impact on adult quality of life.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">Add longitudinal evidence connecting adverse effects to quality of life.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">NONMEDICAL_STIMULANT: common side effects of the drugs include headache, stomach upset, nausea, loss of appetite, trouble sleeping, weight loss, dry mouth, nervousness, mood swings, dizziness, fast heart beat, and heart palpitations
-Location: PDF page 2
-Relevance: Supports stimulant adverse effects, although the paper studies nonmedical college use rather than prescribed treatment at age 32.</t>
+Relevance: Supports stimulant adverse effects, although the paper studies nonmedical college use rather than prescribed treatment at age 32.
+PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -2925,17 +2975,22 @@
       </c>
       <c r="G60" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied paper directly establishes this edge's direction, sign, and stated mechanism for adults around age 45. Pediatric, young-adult, or adjacent evidence is not transferred as midlife causal proof.</t>
+          <t xml:space="preserve">The new medication and observational adult studies do not isolate diagnosis as an intervention reducing functional impairment. Treatment outcomes and clinical assessment recommendations are different exposures.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add midlife adult evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Obtain evidence on recognition and subsequent care with a defined functional endpoint.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.
+BIPOLAR_ADULT: In clinical and research settings, patients screening positive for BSD should be assessed for a possible underlying or coexisting ADHD condition and vice versa.
+Location: Bipolar Symptoms in Adult Attention-Deficit_Hyperactivity Disorder_ A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls.html; article abstract (#article-tabs)
+Relevance: Clinical recommendation for differential assessment; does not establish a quantified increase in misdiagnosis. The abstract specifies ages 18–40 for controls, not the full patient age range.</t>
         </is>
       </c>
     </row>
@@ -2972,19 +3027,25 @@
       </c>
       <c r="G61" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The adult review connects longstanding neuropsychological impairment with negative life outcomes, but does not directly measure quality of life at age 45.</t>
+          <t xml:space="preserve">The prison study directly measures worse QOL alongside ADHD and functional difficulties, and the treatment review measures QOL benefit. These supplement prior life-outcome context without isolating impairment as the cause or establishing a specific-age effect.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain as a qualified pathway and add a midlife quality-of-life measure.</t>
+          <t xml:space="preserve">Retain association-level support and obtain population-representative longitudinal impairment/QOL measurements.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ADULT_CBT: Resulting from their longstanding neuropsychological impairments, such as attentional problems, emotional instability, and disinhibition, they are familiar to a multiplicity of negative life outcomes and under-achievement.
 Location: PDF page 1
-Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.</t>
+Relevance: Supports a relationship between longstanding impairment and adverse adult outcomes without isolating a single causal edge.
+PMID_19270267: The authors conclude that ADHD is common in offenders and is associated with comorbid disorders, worse quality of life, and higher risk for suicidal behaviors.
+Location: Attention deficit hyperactivity disorder in men and women newly committed to prison_ clinical characteristics, psychiatric comorbidity, and quality of life - PubMed.html; article abstract (#eng-abstract)
+Relevance: Selected incarcerated adult sample; not representative of all adults. Association of ADHD with QOL does not isolate functional impairment as a cause or diagnosis as a benefit.
+PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -3021,17 +3082,19 @@
       </c>
       <c r="G62" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied study shows that receiving a diagnosis at midlife itself improves quality of life; any benefit would likely be mediated through effective care and support.</t>
+          <t xml:space="preserve">Medication-associated QOL improvement does not estimate a diagnosis-only effect. The new studies do not compare receipt of diagnosis with no diagnosis while accounting for treatment and support.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Replace the direct edge with explicit treatment and support mediators.</t>
+          <t xml:space="preserve">Retain as unvalidated; make treatment/support mediators explicit instead of inferring a direct diagnostic benefit.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3125,7 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Local PDF</t>
+          <t xml:space="preserve">Local file (PDF or HTML)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
@@ -3599,8 +3662,382 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20925475</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">An 'integrative neuroscience' perspective on ADHD: linking cognition, emotion, brain and genetic measures with implications for clinical support</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/An 'integrative neuroscience' perspective on ADHD_ linking cognition, emotion, brain and genetic measures with implications for clinical support - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">61ac7c7b449a4a20c8d861940094c70f183652541b56724074603e65118f0ce7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_19270267</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention deficit hyperactivity disorder in men and women newly committed to prison: clinical characteristics, psychiatric comorbidity, and quality of life</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Attention deficit hyperactivity disorder in men and women newly committed to prison_ clinical characteristics, psychiatric comorbidity, and quality of life - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">4c226bb161f56d22bb25961dde6761f45708dbca6c9dc6a5bff821d73be84891</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BIPOLAR_ADULT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Bipolar Symptoms in Adult Attention-Deficit/Hyperactivity Disorder: A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Bipolar Symptoms in Adult Attention-Deficit_Hyperactivity Disorder_ A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls.html</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">21d9c13db53d1092a85357c530bdb1c7f62cecedce78f88f9b5fb2ad3432562b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="110" customHeight="1">
+      <c r="A29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20441004</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Can we prevent smoking in children with ADHD: a review of the literature</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Can we prevent smoking in children with ADHD_ a review of the literature - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">5b481cac24cb1945734201bb073efc838f242fec53f2934f6781b315410287ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21206548</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Differences between objective and subjective sleep measures in children with attention deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Differences between objective and subjective sleep measures in children with attention deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">095419b3ac09ece0274c7eb2a752716dbeec8a10f5de279991d2408d6cf40aa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="110" customHeight="1">
+      <c r="A31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21391409</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Disparities in ADHD assessment, diagnosis, and treatment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">e4e39817aefdaebc682ac29916b806dc29215c79ec3b5c582d874706267abc89</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="110" customHeight="1">
+      <c r="A32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21766545</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Effectiveness of nutritional interventions on the functioning of children with ADHD and/or ASD. An updated review of research evidence</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Effectiveness of nutritional interventions on the functioning of children with ADHD and_or ASD. An updated review of research evidence - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">a251eaa1514ee85183cd7fe767e1c822c7635da0ede4aacc84521d76b508b6e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="110" customHeight="1">
+      <c r="A33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21391408</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Geographic analysis of diagnosis of Attention-Deficit/Hyperactivity Disorder in children: Eastern Wisconsin, USA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0039a79c3ff8ab7b5133aa240506d5bbad62bf2c41a1646b8efc827488ec2c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="110" customHeight="1">
+      <c r="A34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20218799</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Neurochemical alterations in women with borderline personality disorder and comorbid attention-deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Neurochemical alterations in women with borderline personality disorder and comorbid attention-deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">fa565ec4b65455fcc706729635a875ad56147454b44f6fb5d32e2b0d30c46637</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="110" customHeight="1">
+      <c r="A35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">CAUDATE_HTML</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Quantitative MR analysis of caudate abnormalities in pediatric ADHD: Proposal for a diagnostic test</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Quantitative MR analysis of caudate abnormalities in pediatric ADHD_ Proposal for a diagnostic test - ClinicalKey.html</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0cd65ad2ea1effde97b96ffdb3151aa1e9cbbe66d67029d44eb0e0a024bd1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="110" customHeight="1">
+      <c r="A36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21117844</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Review of attention-deficit/hyperactivity disorder comorbid with oppositional defiant disorder</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Review of attention-deficit_hyperactivity disorder comorbid with oppositional defiant disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">e751be2e6a9b4100e7f1a40212a6125671c51a59d2404d995579ff1721c80d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="110" customHeight="1">
+      <c r="A37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20410711</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Sex and age differences in attention-deficit/hyperactivity disorder symptoms and diagnoses: implications for DSM-V and ICD-11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Sex and age differences in attention-deficit_hyperactivity disorder symptoms and diagnoses_ implications for DSM-V and ICD-11 - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2352de9c540b1286611714e6803f7e4a1c24daa87abbf9cd0c94a2fa330340df</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="110" customHeight="1">
+      <c r="A38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20513225</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Stimulant drug effects on attention deficit/hyperactivity disorder: a review of the effects of age and sex of patients</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Stimulant drug effects on attention deficit_hyperactivity disorder_ a review of the effects of age and sex of patients - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">836a50e43fa44436663a036460b87348c3216234461498a2fcd9f569bc6a129f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="110" customHeight="1">
+      <c r="A39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20839896</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The impact of medications on quality of life in attention-deficit hyperactivity disorder: a systematic review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">82adf7b51943177cfd8157f1f106ea27247d92e5fc1f95363cf43685ee9bc937</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="110" customHeight="1">
+      <c r="A40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_19482837</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">e2809db8d17b2c5205e0e3ba7e6318737bd7068476739643a4680bf6de6263c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="110" customHeight="1">
+      <c r="A41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20660947</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Event-related potentials associated with error detection in adult ADHD--literature review]</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/[Event-related potentials associated with error detection in adult ADHD--literature review] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f8ad32fc1353f52d6c6e9abccd9b5079433f23369188c86dcfae3f4fcbe12823</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="110" customHeight="1">
+      <c r="A42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20200839</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Population-based diagnostic study to compare the DSM-IV and the Questionnaire for screening Latin American schoolchildren and adolescents for attention deficit hyperactivity disorder]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/[Population-based diagnostic study to compare the DSM-IV and the Questionnaire for screening Latin American schoolchildren and adolescents for attention deficit hyperactivity disorder] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">acc200a656cc542f84a8ed744abd54e1287f5b76edcc0b6cb76230b729b5aa23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:D42"/>
 </worksheet>
 </file>
 
@@ -3631,7 +4068,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2010_45 yo.py, 61 edges, using only the 25 supplied PDF files in 2010 ADHD Papers (24 unique documents; one exact duplicate). Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
+          <t xml:space="preserve">2010_45 yo.py, 61 edges, using 25 supplied PDFs (24 unique PDF documents) and 17 saved HTML article records. Two HTML records reproduce existing PDF studies: 39 unique documents total. Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
         </is>
       </c>
     </row>
@@ -3691,83 +4128,107 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">s12402-010-0036-9 (1).pdf is byte-identical to s12402-010-0036-9.pdf and was counted once as a unique document.</t>
+          <t xml:space="preserve">s12402-010-0036-9 (1).pdf is byte-identical to s12402-010-0036-9.pdf. The sex/age PubMed record (PMID 20410711) and ClinicalKey caudate article reproduce AGE_SEX and CAUDATE_MRI PDFs, respectively. Alternate formats are not independent studies.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="110" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: supported</t>
+          <t xml:space="preserve">html_scope</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
+          <t xml:space="preserve">15 PubMed records and two publisher records were parsed. Only primary article abstracts are used as new evidence; navigation, related articles and saved asset frames are excluded. ClinicalKey also contains the caudate full text, already supplied as PDF. Bipolar publication year is 2010 from the article date and journal citation, despite conflicting website citation metadata. Abstract encoding artifacts are preserved.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="110" customHeight="1">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: partially_supported</t>
+          <t xml:space="preserve">evidence_limits</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
+          <t xml:space="preserve">Cross-sectional associations, selected prison/Tourette populations, clinical disparity commentary, and QOL endpoints are distinguished from causal exposure effects. QOL treatment gains do not validate diagnosis-only benefits or adverse-effect-only harm. Pediatric findings are not transferred to adult age-specific claims.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: contradicted</t>
+          <t xml:space="preserve">Status: supported</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
+          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: mixed_evidence</t>
+          <t xml:space="preserve">Status: partially_supported</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: insufficient_evidence</t>
+          <t xml:space="preserve">Status: contradicted</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
       <c r="A13" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Status: mixed_evidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Status: insufficient_evidence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Status: not_assessable</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="0">
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Undefined variable coding or endpoint makes the proposed direction or sign uninterpretable.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>